--- a/data/fractal_trends_monthly.xlsx
+++ b/data/fractal_trends_monthly.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q123"/>
+  <dimension ref="A1:Q124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,10 +529,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
         <v>24</v>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" t="n">
         <v>21</v>
@@ -641,7 +641,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -694,7 +694,7 @@
         <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -741,10 +741,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
         <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -847,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -900,22 +900,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -953,13 +953,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
         <v>17</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>22</v>
@@ -1171,7 +1171,7 @@
         <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1218,13 +1218,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1321,7 +1321,7 @@
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>59</v>
@@ -1383,7 +1383,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -1498,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1551,16 +1551,16 @@
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1589,22 +1589,22 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
@@ -1654,7 +1654,7 @@
         <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>58</v>
@@ -1707,7 +1707,7 @@
         <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -1748,16 +1748,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
         <v>9</v>
@@ -1772,13 +1772,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -1807,10 +1807,10 @@
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
         <v>7</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1907,16 +1907,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>41</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
         <v>11</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" t="n">
         <v>7</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
         <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
         <v>8</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" t="n">
         <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F39" t="n">
         <v>21</v>
@@ -2543,19 +2543,19 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40" t="n">
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" t="n">
         <v>21</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" t="n">
         <v>18</v>
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>18</v>
@@ -2717,7 +2717,7 @@
         <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2752,25 +2752,25 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
         <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2820,10 +2820,10 @@
         <v>25</v>
       </c>
       <c r="G45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2861,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D46" t="n">
         <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F46" t="n">
         <v>22</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2970,10 +2970,10 @@
         <v>42</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F48" t="n">
         <v>30</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D49" t="n">
         <v>7</v>
@@ -3032,7 +3032,7 @@
         <v>30</v>
       </c>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -3073,13 +3073,13 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D50" t="n">
         <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
         <v>30</v>
@@ -3129,7 +3129,7 @@
         <v>47</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
         <v>15</v>
@@ -3235,7 +3235,7 @@
         <v>50</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
         <v>14</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
         <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G54" t="n">
         <v>16</v>
@@ -3347,7 +3347,7 @@
         <v>14</v>
       </c>
       <c r="F55" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G55" t="n">
         <v>13</v>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
         <v>8</v>
@@ -3403,7 +3403,7 @@
         <v>40</v>
       </c>
       <c r="G56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D57" t="n">
         <v>7</v>
@@ -3547,10 +3547,10 @@
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D59" t="n">
         <v>8</v>
@@ -3559,7 +3559,7 @@
         <v>11</v>
       </c>
       <c r="F59" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G59" t="n">
         <v>8</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D60" t="n">
         <v>6</v>
@@ -3612,10 +3612,10 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -3665,7 +3665,7 @@
         <v>11</v>
       </c>
       <c r="F61" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G61" t="n">
         <v>10</v>
@@ -3674,16 +3674,16 @@
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D62" t="n">
         <v>6</v>
@@ -3718,7 +3718,7 @@
         <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G62" t="n">
         <v>8</v>
@@ -3730,7 +3730,7 @@
         <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D63" t="n">
         <v>5</v>
@@ -3771,10 +3771,10 @@
         <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3783,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -3824,10 +3824,10 @@
         <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>2</v>
@@ -3983,7 +3983,7 @@
         <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G67" t="n">
         <v>4</v>
@@ -4033,13 +4033,13 @@
         <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
         <v>27</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
@@ -4089,10 +4089,10 @@
         <v>7</v>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -4101,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -4133,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
@@ -4195,7 +4195,7 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G71" t="n">
         <v>3</v>
@@ -4354,7 +4354,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G74" t="n">
         <v>5</v>
@@ -4395,7 +4395,7 @@
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
         <v>36</v>
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
         <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G78" t="n">
         <v>4</v>
@@ -4613,7 +4613,7 @@
         <v>25</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
         <v>7</v>
@@ -4625,10 +4625,10 @@
         <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>28</v>
@@ -4713,7 +4713,7 @@
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
         <v>26</v>
@@ -4728,7 +4728,7 @@
         <v>30</v>
       </c>
       <c r="G81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -4740,7 +4740,7 @@
         <v>25</v>
       </c>
       <c r="K81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4769,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D82" t="n">
         <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>27</v>
@@ -4790,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K82" t="n">
         <v>14</v>
@@ -4843,7 +4843,7 @@
         <v>2</v>
       </c>
       <c r="J83" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K83" t="n">
         <v>15</v>
@@ -4878,16 +4878,16 @@
         <v>31</v>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
         <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H84" t="n">
         <v>1</v>
@@ -4925,7 +4925,7 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C85" t="n">
         <v>34</v>
@@ -4955,7 +4955,7 @@
         <v>24</v>
       </c>
       <c r="L85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
         <v>67</v>
       </c>
       <c r="C86" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D86" t="n">
         <v>7</v>
@@ -5002,10 +5002,10 @@
         <v>2</v>
       </c>
       <c r="J86" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L86" t="n">
         <v>14</v>
@@ -5040,7 +5040,7 @@
         <v>7</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
         <v>33</v>
@@ -5058,7 +5058,7 @@
         <v>34</v>
       </c>
       <c r="K87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L87" t="n">
         <v>11</v>
@@ -5084,13 +5084,13 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
         <v>8</v>
@@ -5108,13 +5108,13 @@
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>53</v>
       </c>
       <c r="C89" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D89" t="n">
         <v>5</v>
@@ -5164,7 +5164,7 @@
         <v>26</v>
       </c>
       <c r="K89" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L89" t="n">
         <v>10</v>
@@ -5267,7 +5267,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K91" t="n">
         <v>18</v>
@@ -5296,7 +5296,7 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C92" t="n">
         <v>24</v>
@@ -5323,7 +5323,7 @@
         <v>26</v>
       </c>
       <c r="K92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L92" t="n">
         <v>11</v>
@@ -5352,16 +5352,16 @@
         <v>54</v>
       </c>
       <c r="C93" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D93" t="n">
         <v>7</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G93" t="n">
         <v>7</v>
@@ -5455,7 +5455,7 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C95" t="n">
         <v>22</v>
@@ -5467,7 +5467,7 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
         <v>6</v>
@@ -5476,13 +5476,13 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L95" t="n">
         <v>10</v>
@@ -5508,7 +5508,7 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C96" t="n">
         <v>26</v>
@@ -5523,7 +5523,7 @@
         <v>27</v>
       </c>
       <c r="G96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -5538,7 +5538,7 @@
         <v>26</v>
       </c>
       <c r="L96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M96" t="n">
         <v>25</v>
@@ -5564,7 +5564,7 @@
         <v>54</v>
       </c>
       <c r="C97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D97" t="n">
         <v>6</v>
@@ -5585,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K97" t="n">
         <v>23</v>
@@ -5617,7 +5617,7 @@
         <v>54</v>
       </c>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D98" t="n">
         <v>7</v>
@@ -5641,7 +5641,7 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L98" t="n">
         <v>10</v>
@@ -5670,13 +5670,13 @@
         <v>56</v>
       </c>
       <c r="C99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D99" t="n">
         <v>7</v>
       </c>
       <c r="E99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
         <v>23</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -5720,16 +5720,16 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D100" t="n">
         <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F100" t="n">
         <v>21</v>
@@ -5753,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -5785,13 +5785,13 @@
         <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G101" t="n">
         <v>6</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -5826,10 +5826,10 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D102" t="n">
         <v>6</v>
@@ -5879,7 +5879,7 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C103" t="n">
         <v>19</v>
@@ -5888,16 +5888,16 @@
         <v>7</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F103" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G103" t="n">
         <v>5</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
         <v>18</v>
       </c>
       <c r="K103" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L103" t="n">
         <v>12</v>
@@ -5935,7 +5935,7 @@
         <v>56</v>
       </c>
       <c r="C104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D104" t="n">
         <v>6</v>
@@ -5956,7 +5956,7 @@
         <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K104" t="n">
         <v>18</v>
@@ -5968,7 +5968,7 @@
         <v>27</v>
       </c>
       <c r="N104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -5985,16 +5985,16 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C105" t="n">
         <v>20</v>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F105" t="n">
         <v>20</v>
@@ -6012,13 +6012,13 @@
         <v>18</v>
       </c>
       <c r="K105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L105" t="n">
         <v>10</v>
       </c>
       <c r="M105" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N105" t="n">
         <v>6</v>
@@ -6041,7 +6041,7 @@
         <v>56</v>
       </c>
       <c r="C106" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D106" t="n">
         <v>7</v>
@@ -6059,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J106" t="n">
         <v>22</v>
@@ -6068,7 +6068,7 @@
         <v>20</v>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M106" t="n">
         <v>28</v>
@@ -6083,7 +6083,7 @@
         <v>16</v>
       </c>
       <c r="Q106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -6100,7 +6100,7 @@
         <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F107" t="n">
         <v>22</v>
@@ -6136,7 +6136,7 @@
         <v>10</v>
       </c>
       <c r="Q107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -6144,16 +6144,16 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C108" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D108" t="n">
         <v>8</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F108" t="n">
         <v>29</v>
@@ -6168,13 +6168,13 @@
         <v>8</v>
       </c>
       <c r="J108" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K108" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L108" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M108" t="n">
         <v>34</v>
@@ -6197,7 +6197,7 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C109" t="n">
         <v>30</v>
@@ -6224,13 +6224,13 @@
         <v>22</v>
       </c>
       <c r="K109" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L109" t="n">
         <v>12</v>
       </c>
       <c r="M109" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N109" t="n">
         <v>6</v>
@@ -6239,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -6250,10 +6250,10 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C110" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
         <v>11</v>
       </c>
       <c r="F110" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G110" t="n">
         <v>9</v>
@@ -6274,19 +6274,19 @@
         <v>6</v>
       </c>
       <c r="J110" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K110" t="n">
         <v>22</v>
       </c>
       <c r="L110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M110" t="n">
         <v>33</v>
       </c>
       <c r="N110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -6303,10 +6303,10 @@
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C111" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D111" t="n">
         <v>8</v>
@@ -6315,13 +6315,13 @@
         <v>12</v>
       </c>
       <c r="F111" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G111" t="n">
         <v>8</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>6</v>
@@ -6330,13 +6330,13 @@
         <v>22</v>
       </c>
       <c r="K111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L111" t="n">
         <v>14</v>
       </c>
       <c r="M111" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N111" t="n">
         <v>7</v>
@@ -6356,10 +6356,10 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C112" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D112" t="n">
         <v>8</v>
@@ -6377,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>23</v>
@@ -6401,7 +6401,7 @@
         <v>7</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -6409,7 +6409,7 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C113" t="n">
         <v>28</v>
@@ -6418,7 +6418,7 @@
         <v>7</v>
       </c>
       <c r="E113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F113" t="n">
         <v>24</v>
@@ -6427,7 +6427,7 @@
         <v>7</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
         <v>5</v>
@@ -6436,7 +6436,7 @@
         <v>18</v>
       </c>
       <c r="K113" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L113" t="n">
         <v>13</v>
@@ -6471,10 +6471,10 @@
         <v>6</v>
       </c>
       <c r="E114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F114" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G114" t="n">
         <v>8</v>
@@ -6515,7 +6515,7 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C115" t="n">
         <v>28</v>
@@ -6542,13 +6542,13 @@
         <v>18</v>
       </c>
       <c r="K115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L115" t="n">
         <v>13</v>
       </c>
       <c r="M115" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N115" t="n">
         <v>5</v>
@@ -6568,7 +6568,7 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C116" t="n">
         <v>29</v>
@@ -6580,7 +6580,7 @@
         <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G116" t="n">
         <v>9</v>
@@ -6613,7 +6613,7 @@
         <v>6</v>
       </c>
       <c r="Q116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
@@ -6621,10 +6621,10 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C117" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D117" t="n">
         <v>14</v>
@@ -6633,7 +6633,7 @@
         <v>17</v>
       </c>
       <c r="F117" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G117" t="n">
         <v>12</v>
@@ -6642,19 +6642,19 @@
         <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K117" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L117" t="n">
         <v>18</v>
       </c>
       <c r="M117" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N117" t="n">
         <v>5</v>
@@ -6674,19 +6674,19 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C118" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D118" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E118" t="n">
         <v>18</v>
       </c>
       <c r="F118" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G118" t="n">
         <v>11</v>
@@ -6698,10 +6698,10 @@
         <v>7</v>
       </c>
       <c r="J118" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K118" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L118" t="n">
         <v>14</v>
@@ -6716,7 +6716,7 @@
         <v>7</v>
       </c>
       <c r="P118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q118" t="n">
         <v>15</v>
@@ -6736,19 +6736,19 @@
         <v>14</v>
       </c>
       <c r="E119" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F119" t="n">
         <v>69</v>
       </c>
       <c r="G119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
       </c>
       <c r="I119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J119" t="n">
         <v>27</v>
@@ -6763,7 +6763,7 @@
         <v>31</v>
       </c>
       <c r="N119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
         <v>6</v>
@@ -6780,7 +6780,7 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C120" t="n">
         <v>57</v>
@@ -6804,7 +6804,7 @@
         <v>8</v>
       </c>
       <c r="J120" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K120" t="n">
         <v>46</v>
@@ -6833,10 +6833,10 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C121" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D121" t="n">
         <v>12</v>
@@ -6860,7 +6860,7 @@
         <v>23</v>
       </c>
       <c r="K121" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L121" t="n">
         <v>14</v>
@@ -6886,10 +6886,10 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C122" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D122" t="n">
         <v>10</v>
@@ -6898,7 +6898,7 @@
         <v>14</v>
       </c>
       <c r="F122" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G122" t="n">
         <v>9</v>
@@ -6907,7 +6907,7 @@
         <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>17</v>
@@ -6922,7 +6922,7 @@
         <v>25</v>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O122" t="n">
         <v>6</v>
@@ -6939,52 +6939,105 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C123" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" t="n">
+        <v>13</v>
+      </c>
+      <c r="F123" t="n">
+        <v>29</v>
+      </c>
+      <c r="G123" t="n">
         <v>8</v>
       </c>
-      <c r="E123" t="n">
-        <v>11</v>
-      </c>
-      <c r="F123" t="n">
-        <v>27</v>
-      </c>
-      <c r="G123" t="n">
-        <v>6</v>
-      </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
+        <v>14</v>
+      </c>
+      <c r="K123" t="n">
+        <v>21</v>
+      </c>
+      <c r="L123" t="n">
         <v>12</v>
       </c>
-      <c r="K123" t="n">
-        <v>17</v>
-      </c>
-      <c r="L123" t="n">
-        <v>10</v>
-      </c>
       <c r="M123" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N123" t="n">
         <v>3</v>
       </c>
       <c r="O123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P123" t="n">
         <v>5</v>
       </c>
       <c r="Q123" t="n">
-        <v>24</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B124" t="n">
+        <v>45</v>
+      </c>
+      <c r="C124" t="n">
+        <v>27</v>
+      </c>
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11</v>
+      </c>
+      <c r="F124" t="n">
+        <v>28</v>
+      </c>
+      <c r="G124" t="n">
+        <v>6</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5</v>
+      </c>
+      <c r="J124" t="n">
+        <v>13</v>
+      </c>
+      <c r="K124" t="n">
+        <v>18</v>
+      </c>
+      <c r="L124" t="n">
+        <v>10</v>
+      </c>
+      <c r="M124" t="n">
+        <v>18</v>
+      </c>
+      <c r="N124" t="n">
+        <v>4</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3</v>
+      </c>
+      <c r="P124" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/fractal_trends_monthly.xlsx
+++ b/data/fractal_trends_monthly.xlsx
@@ -529,13 +529,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -635,13 +635,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -703,16 +703,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -741,13 +741,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -809,16 +809,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -900,22 +900,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>19</v>
@@ -1006,13 +1006,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>22</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1165,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -1218,13 +1218,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1324,13 +1324,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1377,13 +1377,13 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -1498,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -1536,16 +1536,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
@@ -1604,7 +1604,7 @@
         <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1642,16 +1642,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1692,25 +1692,25 @@
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D24" t="n">
         <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
         <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1748,19 +1748,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" t="n">
         <v>16</v>
       </c>
-      <c r="F25" t="n">
-        <v>15</v>
-      </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -1769,16 +1769,16 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -1801,13 +1801,13 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D26" t="n">
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
         <v>14</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1863,10 +1863,10 @@
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1960,22 +1960,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
         <v>8</v>
       </c>
-      <c r="E29" t="n">
-        <v>12</v>
-      </c>
-      <c r="F29" t="n">
-        <v>15</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7</v>
-      </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -2066,19 +2066,19 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -2119,16 +2119,16 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" t="n">
         <v>7</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
@@ -2181,13 +2181,13 @@
         <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2225,16 +2225,16 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D34" t="n">
         <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34" t="n">
         <v>7</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
         <v>7</v>
@@ -2287,7 +2287,7 @@
         <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" t="n">
         <v>7</v>
@@ -2331,22 +2331,22 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2384,16 +2384,16 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -2490,22 +2490,22 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D39" t="n">
         <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D40" t="n">
         <v>8</v>
@@ -2555,7 +2555,7 @@
         <v>21</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2596,16 +2596,16 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2649,16 +2649,16 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
         <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42" t="n">
         <v>6</v>
@@ -2702,19 +2702,19 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
         <v>12</v>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -2752,25 +2752,25 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G44" t="n">
         <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2805,19 +2805,19 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D45" t="n">
         <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G45" t="n">
         <v>9</v>
@@ -2861,16 +2861,16 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
         <v>14</v>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G46" t="n">
         <v>8</v>
@@ -2911,25 +2911,25 @@
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D47" t="n">
         <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G47" t="n">
         <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2967,16 +2967,16 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G48" t="n">
         <v>10</v>
@@ -3020,19 +3020,19 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D50" t="n">
         <v>7</v>
@@ -3082,13 +3082,13 @@
         <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3126,22 +3126,22 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F51" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G51" t="n">
         <v>9</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3179,16 +3179,16 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D52" t="n">
         <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G52" t="n">
         <v>8</v>
@@ -3197,10 +3197,10 @@
         <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D53" t="n">
         <v>9</v>
@@ -3241,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G53" t="n">
         <v>15</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F54" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G54" t="n">
         <v>16</v>
@@ -3338,16 +3338,16 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G55" t="n">
         <v>13</v>
@@ -3356,7 +3356,7 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D56" t="n">
         <v>8</v>
@@ -3400,10 +3400,10 @@
         <v>12</v>
       </c>
       <c r="F56" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
@@ -3412,7 +3412,7 @@
         <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D57" t="n">
         <v>7</v>
@@ -3453,10 +3453,10 @@
         <v>12</v>
       </c>
       <c r="F57" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
@@ -3497,16 +3497,16 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G58" t="n">
         <v>9</v>
@@ -3547,19 +3547,19 @@
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D59" t="n">
         <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G59" t="n">
         <v>8</v>
@@ -3600,22 +3600,22 @@
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D60" t="n">
         <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -3656,16 +3656,16 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G61" t="n">
         <v>10</v>
@@ -3674,10 +3674,10 @@
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -3709,16 +3709,16 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D62" t="n">
         <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G62" t="n">
         <v>8</v>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3759,22 +3759,22 @@
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3783,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -3815,19 +3815,19 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D64" t="n">
         <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D65" t="n">
         <v>4</v>
@@ -3877,13 +3877,13 @@
         <v>7</v>
       </c>
       <c r="F65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G65" t="n">
         <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3921,16 +3921,16 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G66" t="n">
         <v>5</v>
@@ -3939,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3974,13 +3974,13 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" t="n">
         <v>23</v>
@@ -3992,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4027,16 +4027,16 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D68" t="n">
         <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G68" t="n">
         <v>4</v>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
@@ -4089,10 +4089,10 @@
         <v>7</v>
       </c>
       <c r="F69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -4101,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -4133,19 +4133,19 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -4154,7 +4154,7 @@
         <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G71" t="n">
         <v>3</v>
@@ -4204,10 +4204,10 @@
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D72" t="n">
         <v>4</v>
@@ -4248,13 +4248,13 @@
         <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>2</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D73" t="n">
         <v>4</v>
@@ -4301,7 +4301,7 @@
         <v>6</v>
       </c>
       <c r="F73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G73" t="n">
         <v>5</v>
@@ -4313,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -4345,16 +4345,16 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
         <v>10</v>
       </c>
       <c r="F74" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G74" t="n">
         <v>5</v>
@@ -4366,7 +4366,7 @@
         <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D75" t="n">
         <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
@@ -4419,7 +4419,7 @@
         <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -4451,16 +4451,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D76" t="n">
         <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F76" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G76" t="n">
         <v>5</v>
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D77" t="n">
         <v>6</v>
@@ -4513,7 +4513,7 @@
         <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G77" t="n">
         <v>5</v>
@@ -4525,7 +4525,7 @@
         <v>2</v>
       </c>
       <c r="J77" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D78" t="n">
         <v>4</v>
@@ -4566,7 +4566,7 @@
         <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G78" t="n">
         <v>4</v>
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -4610,16 +4610,16 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
@@ -4631,10 +4631,10 @@
         <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4663,16 +4663,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G80" t="n">
         <v>4</v>
@@ -4684,10 +4684,10 @@
         <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K80" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D81" t="n">
         <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -4737,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K81" t="n">
         <v>15</v>
@@ -4766,19 +4766,19 @@
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
         <v>8</v>
       </c>
       <c r="F82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G82" t="n">
         <v>7</v>
@@ -4793,7 +4793,7 @@
         <v>25</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4822,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D83" t="n">
         <v>5</v>
@@ -4831,19 +4831,19 @@
         <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K83" t="n">
         <v>15</v>
@@ -4875,34 +4875,34 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G84" t="n">
         <v>12</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
         <v>2</v>
       </c>
       <c r="J84" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K84" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C85" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D85" t="n">
         <v>7</v>
@@ -4937,7 +4937,7 @@
         <v>9</v>
       </c>
       <c r="F85" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G85" t="n">
         <v>10</v>
@@ -4949,13 +4949,13 @@
         <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K85" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L85" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -4978,19 +4978,19 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C86" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G86" t="n">
         <v>9</v>
@@ -5002,13 +5002,13 @@
         <v>2</v>
       </c>
       <c r="J86" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K86" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5031,22 +5031,22 @@
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C87" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D87" t="n">
         <v>7</v>
       </c>
       <c r="E87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F87" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
@@ -5055,10 +5055,10 @@
         <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L87" t="n">
         <v>11</v>
@@ -5084,7 +5084,7 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C88" t="n">
         <v>27</v>
@@ -5096,10 +5096,10 @@
         <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
@@ -5108,10 +5108,10 @@
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L88" t="n">
         <v>11</v>
@@ -5137,19 +5137,19 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G89" t="n">
         <v>8</v>
@@ -5158,16 +5158,16 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D90" t="n">
         <v>5</v>
@@ -5202,28 +5202,28 @@
         <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>25</v>
       </c>
       <c r="K90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L90" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -5243,22 +5243,22 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D91" t="n">
         <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -5267,16 +5267,16 @@
         <v>1</v>
       </c>
       <c r="J91" t="n">
+        <v>22</v>
+      </c>
+      <c r="K91" t="n">
         <v>19</v>
-      </c>
-      <c r="K91" t="n">
-        <v>18</v>
       </c>
       <c r="L91" t="n">
         <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C92" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D92" t="n">
         <v>6</v>
@@ -5308,7 +5308,7 @@
         <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G92" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K92" t="n">
         <v>24</v>
@@ -5329,7 +5329,7 @@
         <v>11</v>
       </c>
       <c r="M92" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C93" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D93" t="n">
         <v>7</v>
@@ -5361,7 +5361,7 @@
         <v>9</v>
       </c>
       <c r="F93" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G93" t="n">
         <v>7</v>
@@ -5370,19 +5370,19 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K93" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M93" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -5402,10 +5402,10 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D94" t="n">
         <v>6</v>
@@ -5414,7 +5414,7 @@
         <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G94" t="n">
         <v>7</v>
@@ -5426,16 +5426,16 @@
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L94" t="n">
         <v>11</v>
       </c>
       <c r="M94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -5455,28 +5455,28 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D95" t="n">
         <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F95" t="n">
         <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>20</v>
@@ -5485,10 +5485,10 @@
         <v>20</v>
       </c>
       <c r="L95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -5508,40 +5508,40 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C96" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
+        <v>28</v>
+      </c>
+      <c r="G96" t="n">
+        <v>7</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>25</v>
+      </c>
+      <c r="K96" t="n">
         <v>27</v>
       </c>
-      <c r="G96" t="n">
-        <v>8</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" t="n">
-        <v>24</v>
-      </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
+        <v>12</v>
+      </c>
+      <c r="M96" t="n">
         <v>26</v>
-      </c>
-      <c r="L96" t="n">
-        <v>11</v>
-      </c>
-      <c r="M96" t="n">
-        <v>25</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -5561,19 +5561,19 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C97" t="n">
         <v>24</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G97" t="n">
         <v>8</v>
@@ -5588,13 +5588,13 @@
         <v>21</v>
       </c>
       <c r="K97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M97" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -5614,25 +5614,25 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C98" t="n">
         <v>26</v>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
         <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G98" t="n">
         <v>7</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -5641,13 +5641,13 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L98" t="n">
         <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -5667,10 +5667,10 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C99" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D99" t="n">
         <v>7</v>
@@ -5679,7 +5679,7 @@
         <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G99" t="n">
         <v>7</v>
@@ -5694,19 +5694,19 @@
         <v>21</v>
       </c>
       <c r="K99" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M99" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C100" t="n">
         <v>24</v>
@@ -5729,10 +5729,10 @@
         <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F100" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G100" t="n">
         <v>7</v>
@@ -5744,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K100" t="n">
         <v>19</v>
@@ -5753,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C101" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D101" t="n">
         <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G101" t="n">
         <v>6</v>
@@ -5797,16 +5797,16 @@
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L101" t="n">
         <v>11</v>
       </c>
       <c r="M101" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
@@ -5826,40 +5826,40 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D102" t="n">
         <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F102" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G102" t="n">
         <v>5</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K102" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M102" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -5879,10 +5879,10 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D103" t="n">
         <v>7</v>
@@ -5891,31 +5891,31 @@
         <v>8</v>
       </c>
       <c r="F103" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K103" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L103" t="n">
         <v>12</v>
       </c>
       <c r="M103" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N103" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -5932,40 +5932,40 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D104" t="n">
         <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F104" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
         <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K104" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L104" t="n">
         <v>11</v>
       </c>
       <c r="M104" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N104" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C105" t="n">
         <v>20</v>
@@ -5997,7 +5997,7 @@
         <v>9</v>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G105" t="n">
         <v>6</v>
@@ -6009,16 +6009,16 @@
         <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K105" t="n">
         <v>19</v>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N105" t="n">
         <v>6</v>
@@ -6038,10 +6038,10 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C106" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D106" t="n">
         <v>7</v>
@@ -6050,10 +6050,10 @@
         <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -6062,7 +6062,7 @@
         <v>14</v>
       </c>
       <c r="J106" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K106" t="n">
         <v>20</v>
@@ -6071,7 +6071,7 @@
         <v>12</v>
       </c>
       <c r="M106" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N106" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
@@ -6091,19 +6091,19 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C107" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E107" t="n">
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G107" t="n">
         <v>6</v>
@@ -6115,16 +6115,16 @@
         <v>8</v>
       </c>
       <c r="J107" t="n">
+        <v>22</v>
+      </c>
+      <c r="K107" t="n">
         <v>21</v>
-      </c>
-      <c r="K107" t="n">
-        <v>20</v>
       </c>
       <c r="L107" t="n">
         <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N107" t="n">
         <v>5</v>
@@ -6133,10 +6133,10 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6144,49 +6144,49 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C108" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E108" t="n">
         <v>11</v>
       </c>
       <c r="F108" t="n">
+        <v>30</v>
+      </c>
+      <c r="G108" t="n">
+        <v>9</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>9</v>
+      </c>
+      <c r="J108" t="n">
+        <v>25</v>
+      </c>
+      <c r="K108" t="n">
         <v>29</v>
       </c>
-      <c r="G108" t="n">
-        <v>8</v>
-      </c>
-      <c r="H108" t="n">
-        <v>1</v>
-      </c>
-      <c r="I108" t="n">
-        <v>8</v>
-      </c>
-      <c r="J108" t="n">
-        <v>23</v>
-      </c>
-      <c r="K108" t="n">
-        <v>28</v>
-      </c>
       <c r="L108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M108" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -6197,10 +6197,10 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C109" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D109" t="n">
         <v>9</v>
@@ -6209,7 +6209,7 @@
         <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G109" t="n">
         <v>10</v>
@@ -6218,31 +6218,31 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K109" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M109" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -6250,19 +6250,19 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C110" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F110" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G110" t="n">
         <v>9</v>
@@ -6271,28 +6271,28 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
+        <v>7</v>
+      </c>
+      <c r="J110" t="n">
+        <v>25</v>
+      </c>
+      <c r="K110" t="n">
+        <v>23</v>
+      </c>
+      <c r="L110" t="n">
+        <v>18</v>
+      </c>
+      <c r="M110" t="n">
+        <v>35</v>
+      </c>
+      <c r="N110" t="n">
         <v>6</v>
       </c>
-      <c r="J110" t="n">
-        <v>24</v>
-      </c>
-      <c r="K110" t="n">
-        <v>22</v>
-      </c>
-      <c r="L110" t="n">
-        <v>17</v>
-      </c>
-      <c r="M110" t="n">
-        <v>33</v>
-      </c>
-      <c r="N110" t="n">
-        <v>5</v>
-      </c>
       <c r="O110" t="n">
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
@@ -6303,43 +6303,43 @@
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C111" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
         <v>6</v>
       </c>
       <c r="J111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M111" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -6356,10 +6356,10 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C112" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D112" t="n">
         <v>8</v>
@@ -6368,28 +6368,28 @@
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L112" t="n">
         <v>14</v>
       </c>
       <c r="M112" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N112" t="n">
         <v>5</v>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
@@ -6409,10 +6409,10 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C113" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D113" t="n">
         <v>7</v>
@@ -6430,10 +6430,10 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K113" t="n">
         <v>22</v>
@@ -6442,7 +6442,7 @@
         <v>13</v>
       </c>
       <c r="M113" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N113" t="n">
         <v>4</v>
@@ -6454,7 +6454,7 @@
         <v>5</v>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6462,10 +6462,10 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C114" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D114" t="n">
         <v>6</v>
@@ -6474,7 +6474,7 @@
         <v>11</v>
       </c>
       <c r="F114" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G114" t="n">
         <v>8</v>
@@ -6483,19 +6483,19 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M114" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N114" t="n">
         <v>5</v>
@@ -6515,10 +6515,10 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C115" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D115" t="n">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G115" t="n">
         <v>8</v>
@@ -6539,16 +6539,16 @@
         <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K115" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L115" t="n">
         <v>13</v>
       </c>
       <c r="M115" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N115" t="n">
         <v>5</v>
@@ -6560,7 +6560,7 @@
         <v>6</v>
       </c>
       <c r="Q115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116">
@@ -6568,19 +6568,19 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C116" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G116" t="n">
         <v>9</v>
@@ -6592,22 +6592,22 @@
         <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M116" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P116" t="n">
         <v>6</v>
@@ -6621,19 +6621,19 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C117" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D117" t="n">
         <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F117" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G117" t="n">
         <v>12</v>
@@ -6645,22 +6645,22 @@
         <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K117" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M117" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P117" t="n">
         <v>7</v>
@@ -6674,19 +6674,19 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C118" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D118" t="n">
         <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F118" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G118" t="n">
         <v>11</v>
@@ -6695,22 +6695,22 @@
         <v>2</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
         <v>27</v>
       </c>
       <c r="K118" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M118" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O118" t="n">
         <v>7</v>
@@ -6719,7 +6719,7 @@
         <v>7</v>
       </c>
       <c r="Q118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119">
@@ -6727,19 +6727,19 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C119" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E119" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F119" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G119" t="n">
         <v>13</v>
@@ -6748,31 +6748,31 @@
         <v>2</v>
       </c>
       <c r="I119" t="n">
+        <v>7</v>
+      </c>
+      <c r="J119" t="n">
+        <v>29</v>
+      </c>
+      <c r="K119" t="n">
+        <v>47</v>
+      </c>
+      <c r="L119" t="n">
+        <v>15</v>
+      </c>
+      <c r="M119" t="n">
+        <v>33</v>
+      </c>
+      <c r="N119" t="n">
         <v>6</v>
-      </c>
-      <c r="J119" t="n">
-        <v>27</v>
-      </c>
-      <c r="K119" t="n">
-        <v>44</v>
-      </c>
-      <c r="L119" t="n">
-        <v>14</v>
-      </c>
-      <c r="M119" t="n">
-        <v>31</v>
-      </c>
-      <c r="N119" t="n">
-        <v>5</v>
       </c>
       <c r="O119" t="n">
         <v>6</v>
       </c>
       <c r="P119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120">
@@ -6780,19 +6780,19 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C120" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D120" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E120" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F120" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G120" t="n">
         <v>12</v>
@@ -6804,16 +6804,16 @@
         <v>8</v>
       </c>
       <c r="J120" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K120" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L120" t="n">
         <v>19</v>
       </c>
       <c r="M120" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N120" t="n">
         <v>6</v>
@@ -6825,7 +6825,7 @@
         <v>9</v>
       </c>
       <c r="Q120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
@@ -6833,22 +6833,22 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C121" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D121" t="n">
         <v>12</v>
       </c>
       <c r="E121" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F121" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H121" t="n">
         <v>3</v>
@@ -6857,16 +6857,16 @@
         <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K121" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L121" t="n">
         <v>14</v>
       </c>
       <c r="M121" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N121" t="n">
         <v>6</v>
@@ -6875,10 +6875,10 @@
         <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q121" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122">
@@ -6886,40 +6886,40 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C122" t="n">
         <v>35</v>
       </c>
       <c r="D122" t="n">
+        <v>11</v>
+      </c>
+      <c r="E122" t="n">
+        <v>15</v>
+      </c>
+      <c r="F122" t="n">
+        <v>42</v>
+      </c>
+      <c r="G122" t="n">
         <v>10</v>
-      </c>
-      <c r="E122" t="n">
-        <v>14</v>
-      </c>
-      <c r="F122" t="n">
-        <v>41</v>
-      </c>
-      <c r="G122" t="n">
-        <v>9</v>
       </c>
       <c r="H122" t="n">
         <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J122" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K122" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L122" t="n">
         <v>13</v>
       </c>
       <c r="M122" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N122" t="n">
         <v>5</v>
@@ -6931,7 +6931,7 @@
         <v>5</v>
       </c>
       <c r="Q122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123">
@@ -6939,19 +6939,19 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C123" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E123" t="n">
         <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G123" t="n">
         <v>8</v>
@@ -6960,22 +6960,22 @@
         <v>3</v>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" t="n">
         <v>14</v>
       </c>
       <c r="K123" t="n">
+        <v>22</v>
+      </c>
+      <c r="L123" t="n">
+        <v>13</v>
+      </c>
+      <c r="M123" t="n">
         <v>21</v>
       </c>
-      <c r="L123" t="n">
-        <v>12</v>
-      </c>
-      <c r="M123" t="n">
-        <v>20</v>
-      </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O123" t="n">
         <v>4</v>
@@ -6984,7 +6984,7 @@
         <v>5</v>
       </c>
       <c r="Q123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124">
@@ -6992,19 +6992,19 @@
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C124" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E124" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F124" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G124" t="n">
         <v>6</v>
@@ -7013,25 +7013,25 @@
         <v>2</v>
       </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K124" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L124" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M124" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N124" t="n">
         <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P124" t="n">
         <v>4</v>

--- a/data/fractal_trends_monthly.xlsx
+++ b/data/fractal_trends_monthly.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,14 +529,14 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
         <v>23</v>
       </c>
-      <c r="E2" t="n">
-        <v>25</v>
-      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -635,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -703,16 +703,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -741,10 +741,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -844,13 +844,13 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>21</v>
@@ -900,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
         <v>19</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1021,13 +1021,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1165,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1218,19 +1218,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1271,13 +1271,13 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1321,16 +1321,16 @@
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>19</v>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1536,28 +1536,28 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1589,22 +1589,22 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1642,16 +1642,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1695,22 +1695,22 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1748,22 +1748,22 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" t="n">
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -1801,16 +1801,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D26" t="n">
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
         <v>7</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1916,7 +1916,7 @@
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29" t="n">
         <v>9</v>
@@ -1969,19 +1969,19 @@
         <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
@@ -2075,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
         <v>7</v>
@@ -2119,16 +2119,16 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
         <v>7</v>
@@ -2140,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
@@ -2181,19 +2181,19 @@
         <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2225,19 +2225,19 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D34" t="n">
         <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2275,19 +2275,19 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
         <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
         <v>7</v>
@@ -2331,19 +2331,19 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
         <v>23</v>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -2384,16 +2384,16 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
@@ -2437,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -2490,22 +2490,22 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
         <v>14</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G39" t="n">
         <v>7</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2549,7 +2549,7 @@
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
         <v>21</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
@@ -2605,7 +2605,7 @@
         <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
@@ -2649,16 +2649,16 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
         <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G42" t="n">
         <v>6</v>
@@ -2702,22 +2702,22 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G43" t="n">
         <v>7</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2755,16 +2755,16 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
         <v>8</v>
@@ -2805,19 +2805,19 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D45" t="n">
         <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G45" t="n">
         <v>9</v>
@@ -2861,16 +2861,16 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
         <v>14</v>
       </c>
       <c r="F46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G46" t="n">
         <v>8</v>
@@ -2911,19 +2911,19 @@
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D47" t="n">
         <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G47" t="n">
         <v>8</v>
@@ -2967,16 +2967,16 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D48" t="n">
         <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G48" t="n">
         <v>10</v>
@@ -3020,19 +3020,19 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3073,22 +3073,22 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D50" t="n">
         <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3126,22 +3126,22 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D51" t="n">
         <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G51" t="n">
         <v>9</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3179,16 +3179,16 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G52" t="n">
         <v>8</v>
@@ -3197,10 +3197,10 @@
         <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3232,22 +3232,22 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
         <v>14</v>
       </c>
       <c r="F53" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G53" t="n">
         <v>15</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>9</v>
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
@@ -3294,10 +3294,10 @@
         <v>16</v>
       </c>
       <c r="F54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G54" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H54" t="n">
         <v>2</v>
@@ -3338,16 +3338,16 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F55" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G55" t="n">
         <v>13</v>
@@ -3356,7 +3356,7 @@
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D56" t="n">
         <v>8</v>
@@ -3400,7 +3400,7 @@
         <v>12</v>
       </c>
       <c r="F56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G56" t="n">
         <v>12</v>
@@ -3412,7 +3412,7 @@
         <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D57" t="n">
         <v>7</v>
@@ -3453,10 +3453,10 @@
         <v>12</v>
       </c>
       <c r="F57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
@@ -3497,16 +3497,16 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G58" t="n">
         <v>9</v>
@@ -3550,16 +3550,16 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D59" t="n">
         <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F59" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G59" t="n">
         <v>8</v>
@@ -3600,16 +3600,16 @@
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D60" t="n">
         <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F60" t="n">
         <v>57</v>
@@ -3656,16 +3656,16 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G61" t="n">
         <v>10</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D62" t="n">
         <v>6</v>
@@ -3718,7 +3718,7 @@
         <v>11</v>
       </c>
       <c r="F62" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G62" t="n">
         <v>8</v>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3762,22 +3762,22 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -3815,16 +3815,16 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G64" t="n">
         <v>6</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D65" t="n">
         <v>4</v>
@@ -3877,7 +3877,7 @@
         <v>7</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G65" t="n">
         <v>5</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3921,16 +3921,16 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G66" t="n">
         <v>5</v>
@@ -3939,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3974,13 +3974,13 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67" t="n">
         <v>23</v>
@@ -3992,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4024,10 +4024,10 @@
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D68" t="n">
         <v>4</v>
@@ -4036,7 +4036,7 @@
         <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G68" t="n">
         <v>4</v>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
@@ -4089,7 +4089,7 @@
         <v>7</v>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -4101,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -4133,19 +4133,19 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -4154,7 +4154,7 @@
         <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
@@ -4207,7 +4207,7 @@
         <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -4248,10 +4248,10 @@
         <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D73" t="n">
         <v>4</v>
@@ -4301,7 +4301,7 @@
         <v>6</v>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G73" t="n">
         <v>5</v>
@@ -4345,28 +4345,28 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G74" t="n">
         <v>5</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
         <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D75" t="n">
         <v>6</v>
@@ -4407,10 +4407,10 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
@@ -4419,7 +4419,7 @@
         <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -4451,16 +4451,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D76" t="n">
         <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G76" t="n">
         <v>5</v>
@@ -4472,7 +4472,7 @@
         <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D77" t="n">
         <v>6</v>
@@ -4513,7 +4513,7 @@
         <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G77" t="n">
         <v>5</v>
@@ -4525,7 +4525,7 @@
         <v>2</v>
       </c>
       <c r="J77" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -4557,16 +4557,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
         <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G78" t="n">
         <v>4</v>
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D79" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
@@ -4631,10 +4631,10 @@
         <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4663,16 +4663,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
         <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G80" t="n">
         <v>4</v>
@@ -4681,13 +4681,13 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K80" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4716,19 +4716,19 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D81" t="n">
         <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F81" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -4737,10 +4737,10 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -4766,19 +4766,19 @@
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
         <v>8</v>
       </c>
       <c r="F82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G82" t="n">
         <v>7</v>
@@ -4790,10 +4790,10 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4822,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D83" t="n">
         <v>5</v>
@@ -4831,19 +4831,19 @@
         <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H83" t="n">
         <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K83" t="n">
         <v>15</v>
@@ -4875,34 +4875,34 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G84" t="n">
         <v>12</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
         <v>2</v>
       </c>
       <c r="J84" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L84" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C85" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D85" t="n">
         <v>7</v>
@@ -4937,7 +4937,7 @@
         <v>9</v>
       </c>
       <c r="F85" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G85" t="n">
         <v>10</v>
@@ -4949,13 +4949,13 @@
         <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K85" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L85" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -4978,19 +4978,19 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C86" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G86" t="n">
         <v>9</v>
@@ -5002,13 +5002,13 @@
         <v>2</v>
       </c>
       <c r="J86" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L86" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C87" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D87" t="n">
         <v>7</v>
@@ -5043,10 +5043,10 @@
         <v>10</v>
       </c>
       <c r="F87" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
@@ -5055,10 +5055,10 @@
         <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K87" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L87" t="n">
         <v>11</v>
@@ -5067,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C88" t="n">
         <v>27</v>
@@ -5096,25 +5096,25 @@
         <v>8</v>
       </c>
       <c r="F88" t="n">
+        <v>31</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
         <v>32</v>
       </c>
-      <c r="G88" t="n">
-        <v>9</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" t="n">
-        <v>33</v>
-      </c>
       <c r="K88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5137,19 +5137,19 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C89" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G89" t="n">
         <v>8</v>
@@ -5158,16 +5158,16 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K89" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -5190,7 +5190,7 @@
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C90" t="n">
         <v>24</v>
@@ -5202,7 +5202,7 @@
         <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G90" t="n">
         <v>7</v>
@@ -5211,16 +5211,16 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>25</v>
       </c>
       <c r="K90" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M90" t="n">
         <v>8</v>
@@ -5243,10 +5243,10 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C91" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D91" t="n">
         <v>6</v>
@@ -5255,10 +5255,10 @@
         <v>7</v>
       </c>
       <c r="F91" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -5267,16 +5267,16 @@
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K91" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L91" t="n">
         <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D92" t="n">
         <v>6</v>
@@ -5308,7 +5308,7 @@
         <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G92" t="n">
         <v>10</v>
@@ -5320,16 +5320,16 @@
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K92" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M92" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -5349,19 +5349,19 @@
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C93" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D93" t="n">
         <v>7</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G93" t="n">
         <v>7</v>
@@ -5370,19 +5370,19 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>25</v>
       </c>
       <c r="K93" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M93" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -5402,10 +5402,10 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D94" t="n">
         <v>6</v>
@@ -5414,7 +5414,7 @@
         <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G94" t="n">
         <v>7</v>
@@ -5426,16 +5426,16 @@
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L94" t="n">
         <v>11</v>
       </c>
       <c r="M94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -5455,22 +5455,22 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C95" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D95" t="n">
         <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F95" t="n">
         <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
@@ -5479,16 +5479,16 @@
         <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -5508,19 +5508,19 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C96" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F96" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G96" t="n">
         <v>7</v>
@@ -5532,16 +5532,16 @@
         <v>1</v>
       </c>
       <c r="J96" t="n">
+        <v>23</v>
+      </c>
+      <c r="K96" t="n">
         <v>25</v>
       </c>
-      <c r="K96" t="n">
-        <v>27</v>
-      </c>
       <c r="L96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -5561,40 +5561,40 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C97" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D97" t="n">
+        <v>6</v>
+      </c>
+      <c r="E97" t="n">
+        <v>9</v>
+      </c>
+      <c r="F97" t="n">
+        <v>22</v>
+      </c>
+      <c r="G97" t="n">
         <v>7</v>
       </c>
-      <c r="E97" t="n">
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>20</v>
+      </c>
+      <c r="K97" t="n">
+        <v>23</v>
+      </c>
+      <c r="L97" t="n">
         <v>10</v>
       </c>
-      <c r="F97" t="n">
-        <v>24</v>
-      </c>
-      <c r="G97" t="n">
-        <v>8</v>
-      </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" t="n">
-        <v>21</v>
-      </c>
-      <c r="K97" t="n">
-        <v>24</v>
-      </c>
-      <c r="L97" t="n">
-        <v>11</v>
-      </c>
       <c r="M97" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -5614,40 +5614,40 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C98" t="n">
         <v>26</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E98" t="n">
         <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G98" t="n">
         <v>7</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
       </c>
       <c r="J98" t="n">
+        <v>19</v>
+      </c>
+      <c r="K98" t="n">
         <v>20</v>
-      </c>
-      <c r="K98" t="n">
-        <v>21</v>
       </c>
       <c r="L98" t="n">
         <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -5667,22 +5667,22 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C99" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D99" t="n">
         <v>7</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F99" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -5694,19 +5694,19 @@
         <v>21</v>
       </c>
       <c r="K99" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L99" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M99" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C100" t="n">
         <v>24</v>
@@ -5729,10 +5729,10 @@
         <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F100" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G100" t="n">
         <v>7</v>
@@ -5744,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K100" t="n">
         <v>19</v>
@@ -5753,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C101" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D101" t="n">
         <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G101" t="n">
         <v>6</v>
@@ -5797,16 +5797,16 @@
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K101" t="n">
         <v>18</v>
       </c>
       <c r="L101" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M101" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
@@ -5826,40 +5826,40 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D102" t="n">
         <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F102" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G102" t="n">
         <v>5</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M102" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -5879,43 +5879,43 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C103" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D103" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" t="n">
         <v>7</v>
       </c>
-      <c r="E103" t="n">
-        <v>8</v>
-      </c>
       <c r="F103" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G103" t="n">
         <v>6</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K103" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L103" t="n">
         <v>12</v>
       </c>
       <c r="M103" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N103" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -5932,22 +5932,22 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D104" t="n">
         <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H104" t="n">
         <v>1</v>
@@ -5956,19 +5956,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="n">
+        <v>17</v>
+      </c>
+      <c r="K104" t="n">
         <v>18</v>
-      </c>
-      <c r="K104" t="n">
-        <v>19</v>
       </c>
       <c r="L104" t="n">
         <v>11</v>
       </c>
       <c r="M104" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5985,7 +5985,7 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C105" t="n">
         <v>20</v>
@@ -5997,28 +5997,28 @@
         <v>9</v>
       </c>
       <c r="F105" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G105" t="n">
         <v>6</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K105" t="n">
         <v>19</v>
       </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M105" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N105" t="n">
         <v>6</v>
@@ -6038,7 +6038,7 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C106" t="n">
         <v>25</v>
@@ -6050,10 +6050,10 @@
         <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -6068,10 +6068,10 @@
         <v>20</v>
       </c>
       <c r="L106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N106" t="n">
         <v>5</v>
@@ -6080,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
@@ -6091,19 +6091,19 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C107" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G107" t="n">
         <v>6</v>
@@ -6115,16 +6115,16 @@
         <v>8</v>
       </c>
       <c r="J107" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K107" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L107" t="n">
         <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N107" t="n">
         <v>5</v>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q107" t="n">
         <v>1</v>
@@ -6144,49 +6144,49 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C108" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D108" t="n">
         <v>9</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J108" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K108" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L108" t="n">
+        <v>12</v>
+      </c>
+      <c r="M108" t="n">
+        <v>34</v>
+      </c>
+      <c r="N108" t="n">
+        <v>5</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
         <v>13</v>
-      </c>
-      <c r="M108" t="n">
-        <v>35</v>
-      </c>
-      <c r="N108" t="n">
-        <v>6</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>14</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -6197,10 +6197,10 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C109" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D109" t="n">
         <v>9</v>
@@ -6209,31 +6209,31 @@
         <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G109" t="n">
         <v>10</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J109" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K109" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M109" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -6250,10 +6250,10 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C110" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
         <v>12</v>
       </c>
       <c r="F110" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G110" t="n">
         <v>9</v>
@@ -6271,19 +6271,19 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K110" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L110" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M110" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N110" t="n">
         <v>6</v>
@@ -6292,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
@@ -6303,43 +6303,43 @@
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C111" t="n">
+        <v>27</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
+      </c>
+      <c r="E111" t="n">
+        <v>12</v>
+      </c>
+      <c r="F111" t="n">
         <v>29</v>
       </c>
-      <c r="D111" t="n">
-        <v>9</v>
-      </c>
-      <c r="E111" t="n">
-        <v>13</v>
-      </c>
-      <c r="F111" t="n">
-        <v>32</v>
-      </c>
       <c r="G111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>6</v>
       </c>
       <c r="J111" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K111" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L111" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M111" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -6356,10 +6356,10 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C112" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D112" t="n">
         <v>8</v>
@@ -6368,7 +6368,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G112" t="n">
         <v>9</v>
@@ -6377,19 +6377,19 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K112" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L112" t="n">
         <v>14</v>
       </c>
       <c r="M112" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N112" t="n">
         <v>5</v>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
@@ -6409,10 +6409,10 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C113" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D113" t="n">
         <v>7</v>
@@ -6424,25 +6424,25 @@
         <v>24</v>
       </c>
       <c r="G113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H113" t="n">
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J113" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K113" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L113" t="n">
         <v>13</v>
       </c>
       <c r="M113" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N113" t="n">
         <v>4</v>
@@ -6454,7 +6454,7 @@
         <v>5</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -6462,10 +6462,10 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C114" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D114" t="n">
         <v>6</v>
@@ -6474,7 +6474,7 @@
         <v>11</v>
       </c>
       <c r="F114" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G114" t="n">
         <v>8</v>
@@ -6483,19 +6483,19 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K114" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L114" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M114" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N114" t="n">
         <v>5</v>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q114" t="n">
         <v>2</v>
@@ -6515,10 +6515,10 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C115" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D115" t="n">
         <v>8</v>
@@ -6527,7 +6527,7 @@
         <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G115" t="n">
         <v>8</v>
@@ -6539,16 +6539,16 @@
         <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K115" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L115" t="n">
         <v>13</v>
       </c>
       <c r="M115" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N115" t="n">
         <v>5</v>
@@ -6560,7 +6560,7 @@
         <v>6</v>
       </c>
       <c r="Q115" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
@@ -6568,7 +6568,7 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C116" t="n">
         <v>30</v>
@@ -6580,7 +6580,7 @@
         <v>11</v>
       </c>
       <c r="F116" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G116" t="n">
         <v>9</v>
@@ -6592,16 +6592,16 @@
         <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K116" t="n">
         <v>23</v>
       </c>
       <c r="L116" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M116" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N116" t="n">
         <v>5</v>
@@ -6624,43 +6624,43 @@
         <v>100</v>
       </c>
       <c r="C117" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D117" t="n">
         <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F117" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G117" t="n">
         <v>12</v>
       </c>
       <c r="H117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
         <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K117" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L117" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M117" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N117" t="n">
         <v>6</v>
       </c>
       <c r="O117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P117" t="n">
         <v>7</v>
@@ -6674,19 +6674,19 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C118" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D118" t="n">
         <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F118" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G118" t="n">
         <v>11</v>
@@ -6701,25 +6701,25 @@
         <v>27</v>
       </c>
       <c r="K118" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L118" t="n">
         <v>15</v>
       </c>
       <c r="M118" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
         <v>7</v>
       </c>
       <c r="P118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q118" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119">
@@ -6727,19 +6727,19 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C119" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D119" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E119" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F119" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G119" t="n">
         <v>13</v>
@@ -6751,16 +6751,16 @@
         <v>7</v>
       </c>
       <c r="J119" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K119" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L119" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M119" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N119" t="n">
         <v>6</v>
@@ -6772,7 +6772,7 @@
         <v>7</v>
       </c>
       <c r="Q119" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
@@ -6780,19 +6780,19 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C120" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D120" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E120" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G120" t="n">
         <v>12</v>
@@ -6804,16 +6804,16 @@
         <v>8</v>
       </c>
       <c r="J120" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K120" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L120" t="n">
         <v>19</v>
       </c>
       <c r="M120" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N120" t="n">
         <v>6</v>
@@ -6825,7 +6825,7 @@
         <v>9</v>
       </c>
       <c r="Q120" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121">
@@ -6836,37 +6836,37 @@
         <v>82</v>
       </c>
       <c r="C121" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D121" t="n">
         <v>12</v>
       </c>
       <c r="E121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F121" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
         <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K121" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L121" t="n">
         <v>14</v>
       </c>
       <c r="M121" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N121" t="n">
         <v>6</v>
@@ -6878,7 +6878,7 @@
         <v>6</v>
       </c>
       <c r="Q121" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122">
@@ -6886,22 +6886,22 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C122" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F122" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H122" t="n">
         <v>2</v>
@@ -6910,16 +6910,16 @@
         <v>5</v>
       </c>
       <c r="J122" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L122" t="n">
         <v>13</v>
       </c>
       <c r="M122" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N122" t="n">
         <v>5</v>
@@ -6931,7 +6931,7 @@
         <v>5</v>
       </c>
       <c r="Q122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
@@ -6939,43 +6939,43 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C123" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E123" t="n">
         <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G123" t="n">
         <v>8</v>
       </c>
       <c r="H123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>14</v>
       </c>
       <c r="K123" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L123" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M123" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
         <v>4</v>
@@ -6995,7 +6995,7 @@
         <v>50</v>
       </c>
       <c r="C124" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D124" t="n">
         <v>9</v>
@@ -7004,7 +7004,7 @@
         <v>13</v>
       </c>
       <c r="F124" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G124" t="n">
         <v>6</v>
@@ -7019,25 +7019,78 @@
         <v>14</v>
       </c>
       <c r="K124" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M124" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N124" t="n">
         <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P124" t="n">
         <v>4</v>
       </c>
       <c r="Q124" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B125" t="n">
+        <v>39</v>
+      </c>
+      <c r="C125" t="n">
+        <v>26</v>
+      </c>
+      <c r="D125" t="n">
+        <v>10</v>
+      </c>
+      <c r="E125" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" t="n">
+        <v>28</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5</v>
+      </c>
+      <c r="J125" t="n">
+        <v>7</v>
+      </c>
+      <c r="K125" t="n">
+        <v>19</v>
+      </c>
+      <c r="L125" t="n">
+        <v>10</v>
+      </c>
+      <c r="M125" t="n">
+        <v>16</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3</v>
+      </c>
+      <c r="P125" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/fractal_trends_monthly.xlsx
+++ b/data/fractal_trends_monthly.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q125"/>
+  <dimension ref="A1:Q130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
         <v>21</v>
@@ -579,13 +579,13 @@
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
@@ -635,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
@@ -685,10 +685,10 @@
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" t="n">
         <v>17</v>
@@ -741,13 +741,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
         <v>19</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -847,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -900,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -953,13 +953,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" t="n">
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>19</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
         <v>22</v>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1112,13 +1112,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1215,22 +1215,22 @@
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1321,16 +1321,16 @@
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
         <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -1498,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1536,19 +1536,19 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1601,10 +1601,10 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1642,10 +1642,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1695,13 +1695,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D24" t="n">
         <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
         <v>16</v>
@@ -1710,10 +1710,10 @@
         <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1748,22 +1748,22 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -1801,10 +1801,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
         <v>15</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1863,7 +1863,7 @@
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
         <v>8</v>
@@ -1907,13 +1907,13 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
@@ -1960,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
@@ -1975,13 +1975,13 @@
         <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2066,19 +2066,19 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" t="n">
         <v>7</v>
@@ -2128,7 +2128,7 @@
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="n">
         <v>7</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2172,16 +2172,16 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" t="n">
         <v>8</v>
@@ -2237,7 +2237,7 @@
         <v>16</v>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2275,25 +2275,25 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>46</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G35" t="n">
         <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2340,13 +2340,13 @@
         <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
         <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2384,28 +2384,28 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2437,22 +2437,22 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" t="n">
         <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G38" t="n">
         <v>8</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
         <v>7</v>
@@ -2502,7 +2502,7 @@
         <v>20</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" t="n">
         <v>8</v>
@@ -2552,10 +2552,10 @@
         <v>12</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
         <v>18</v>
@@ -2649,22 +2649,22 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D42" t="n">
         <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G42" t="n">
         <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
         <v>6</v>
@@ -2711,13 +2711,13 @@
         <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
@@ -2767,7 +2767,7 @@
         <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" t="n">
         <v>7</v>
@@ -2817,10 +2817,10 @@
         <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -2861,16 +2861,16 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" t="n">
         <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G46" t="n">
         <v>8</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2914,19 +2914,19 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D47" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21</v>
+      </c>
+      <c r="G47" t="n">
         <v>7</v>
-      </c>
-      <c r="E47" t="n">
-        <v>13</v>
-      </c>
-      <c r="F47" t="n">
-        <v>22</v>
-      </c>
-      <c r="G47" t="n">
-        <v>8</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
@@ -2967,22 +2967,22 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
         <v>14</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G48" t="n">
         <v>10</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D49" t="n">
         <v>7</v>
@@ -3029,7 +3029,7 @@
         <v>14</v>
       </c>
       <c r="F49" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G49" t="n">
         <v>11</v>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D50" t="n">
         <v>7</v>
@@ -3082,7 +3082,7 @@
         <v>14</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G50" t="n">
         <v>10</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D51" t="n">
         <v>8</v>
@@ -3179,25 +3179,25 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D52" t="n">
         <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
         <v>23</v>
       </c>
       <c r="G52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3232,28 +3232,28 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D53" t="n">
         <v>8</v>
       </c>
       <c r="E53" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" t="n">
+        <v>38</v>
+      </c>
+      <c r="G53" t="n">
         <v>14</v>
       </c>
-      <c r="F53" t="n">
-        <v>39</v>
-      </c>
-      <c r="G53" t="n">
-        <v>15</v>
-      </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -3285,16 +3285,16 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G54" t="n">
         <v>15</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" t="n">
         <v>8</v>
@@ -3347,10 +3347,10 @@
         <v>14</v>
       </c>
       <c r="F55" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H55" t="n">
         <v>2</v>
@@ -3391,19 +3391,19 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D56" t="n">
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
@@ -3444,16 +3444,16 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D57" t="n">
         <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G57" t="n">
         <v>10</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D58" t="n">
         <v>6</v>
@@ -3506,7 +3506,7 @@
         <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G58" t="n">
         <v>9</v>
@@ -3515,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D59" t="n">
         <v>8</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D60" t="n">
         <v>6</v>
@@ -3612,10 +3612,10 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -3656,25 +3656,25 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D61" t="n">
         <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F61" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H61" t="n">
         <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3709,16 +3709,16 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G62" t="n">
         <v>8</v>
@@ -3727,7 +3727,7 @@
         <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D63" t="n">
         <v>5</v>
@@ -3771,13 +3771,13 @@
         <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G63" t="n">
         <v>5</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
         <v>4</v>
@@ -3824,10 +3824,10 @@
         <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D65" t="n">
         <v>4</v>
@@ -3877,7 +3877,7 @@
         <v>7</v>
       </c>
       <c r="F65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G65" t="n">
         <v>5</v>
@@ -3921,19 +3921,19 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D66" t="n">
         <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
@@ -3980,10 +3980,10 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G67" t="n">
         <v>4</v>
@@ -4024,22 +4024,22 @@
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
         <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -4080,16 +4080,16 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -4098,10 +4098,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -4133,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
@@ -4142,7 +4142,7 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G70" t="n">
         <v>3</v>
@@ -4192,10 +4192,10 @@
         <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G71" t="n">
         <v>3</v>
@@ -4239,16 +4239,16 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D72" t="n">
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
         <v>4</v>
@@ -4289,22 +4289,22 @@
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D73" t="n">
         <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73" t="n">
         <v>1</v>
@@ -4313,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D74" t="n">
         <v>5</v>
@@ -4354,19 +4354,19 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G74" t="n">
         <v>5</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -4398,16 +4398,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D75" t="n">
         <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G75" t="n">
         <v>5</v>
@@ -4419,7 +4419,7 @@
         <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D76" t="n">
         <v>6</v>
@@ -4460,7 +4460,7 @@
         <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G76" t="n">
         <v>5</v>
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4501,19 +4501,19 @@
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
+        <v>30</v>
+      </c>
+      <c r="D77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>8</v>
+      </c>
+      <c r="F77" t="n">
         <v>32</v>
-      </c>
-      <c r="D77" t="n">
-        <v>6</v>
-      </c>
-      <c r="E77" t="n">
-        <v>9</v>
-      </c>
-      <c r="F77" t="n">
-        <v>33</v>
       </c>
       <c r="G77" t="n">
         <v>5</v>
@@ -4522,10 +4522,10 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -4557,16 +4557,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
         <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G78" t="n">
         <v>4</v>
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -4610,16 +4610,16 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D79" t="n">
         <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
@@ -4663,16 +4663,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D80" t="n">
         <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G80" t="n">
         <v>4</v>
@@ -4681,13 +4681,13 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K80" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4725,7 +4725,7 @@
         <v>7</v>
       </c>
       <c r="F81" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G81" t="n">
         <v>7</v>
@@ -4737,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K81" t="n">
         <v>14</v>
@@ -4752,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -4775,13 +4775,13 @@
         <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>26</v>
       </c>
       <c r="G82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
@@ -4790,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K82" t="n">
         <v>14</v>
@@ -4822,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D83" t="n">
         <v>5</v>
@@ -4831,7 +4831,7 @@
         <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G83" t="n">
         <v>6</v>
@@ -4843,10 +4843,10 @@
         <v>2</v>
       </c>
       <c r="J83" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K83" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D84" t="n">
         <v>6</v>
@@ -4884,7 +4884,7 @@
         <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G84" t="n">
         <v>12</v>
@@ -4893,16 +4893,16 @@
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K84" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L84" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -4925,19 +4925,19 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C85" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D85" t="n">
         <v>7</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F85" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G85" t="n">
         <v>10</v>
@@ -4949,13 +4949,13 @@
         <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K85" t="n">
         <v>24</v>
       </c>
       <c r="L85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C86" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D86" t="n">
         <v>7</v>
@@ -4990,7 +4990,7 @@
         <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G86" t="n">
         <v>9</v>
@@ -5002,10 +5002,10 @@
         <v>2</v>
       </c>
       <c r="J86" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L86" t="n">
         <v>14</v>
@@ -5034,16 +5034,16 @@
         <v>74</v>
       </c>
       <c r="C87" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D87" t="n">
         <v>7</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G87" t="n">
         <v>9</v>
@@ -5055,10 +5055,10 @@
         <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K87" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L87" t="n">
         <v>11</v>
@@ -5067,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -5084,19 +5084,19 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C88" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
         <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G88" t="n">
         <v>8</v>
@@ -5108,10 +5108,10 @@
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L88" t="n">
         <v>10</v>
@@ -5137,10 +5137,10 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D89" t="n">
         <v>5</v>
@@ -5149,7 +5149,7 @@
         <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G89" t="n">
         <v>8</v>
@@ -5161,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K89" t="n">
         <v>18</v>
@@ -5190,10 +5190,10 @@
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C90" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>5</v>
@@ -5202,28 +5202,28 @@
         <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K90" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L90" t="n">
         <v>13</v>
       </c>
       <c r="M90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -5243,19 +5243,19 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C91" t="n">
         <v>22</v>
       </c>
       <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="n">
         <v>6</v>
       </c>
-      <c r="E91" t="n">
-        <v>7</v>
-      </c>
       <c r="F91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G91" t="n">
         <v>7</v>
@@ -5270,13 +5270,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L91" t="n">
         <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5296,40 +5296,40 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C92" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
         <v>8</v>
       </c>
       <c r="F92" t="n">
+        <v>24</v>
+      </c>
+      <c r="G92" t="n">
+        <v>9</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
         <v>25</v>
       </c>
-      <c r="G92" t="n">
-        <v>10</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="n">
-        <v>26</v>
-      </c>
       <c r="K92" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L92" t="n">
         <v>10</v>
       </c>
       <c r="M92" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -5349,13 +5349,13 @@
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
         <v>8</v>
@@ -5370,19 +5370,19 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L93" t="n">
         <v>12</v>
       </c>
       <c r="M93" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -5402,31 +5402,31 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C94" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F94" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G94" t="n">
         <v>7</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K94" t="n">
         <v>19</v>
@@ -5435,7 +5435,7 @@
         <v>11</v>
       </c>
       <c r="M94" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -5455,10 +5455,10 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D95" t="n">
         <v>6</v>
@@ -5467,7 +5467,7 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G95" t="n">
         <v>6</v>
@@ -5482,13 +5482,13 @@
         <v>19</v>
       </c>
       <c r="K95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L95" t="n">
         <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -5508,10 +5508,10 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
@@ -5541,7 +5541,7 @@
         <v>11</v>
       </c>
       <c r="M96" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C97" t="n">
         <v>23</v>
@@ -5588,13 +5588,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L97" t="n">
         <v>10</v>
       </c>
       <c r="M97" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -5614,10 +5614,10 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C98" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D98" t="n">
         <v>7</v>
@@ -5626,7 +5626,7 @@
         <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G98" t="n">
         <v>7</v>
@@ -5647,7 +5647,7 @@
         <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -5667,10 +5667,10 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C99" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D99" t="n">
         <v>7</v>
@@ -5679,10 +5679,10 @@
         <v>9</v>
       </c>
       <c r="F99" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -5691,13 +5691,13 @@
         <v>2</v>
       </c>
       <c r="J99" t="n">
+        <v>20</v>
+      </c>
+      <c r="K99" t="n">
         <v>21</v>
       </c>
-      <c r="K99" t="n">
-        <v>22</v>
-      </c>
       <c r="L99" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M99" t="n">
         <v>32</v>
@@ -5706,13 +5706,13 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -5720,10 +5720,10 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C100" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D100" t="n">
         <v>6</v>
@@ -5735,7 +5735,7 @@
         <v>20</v>
       </c>
       <c r="G100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
@@ -5744,16 +5744,16 @@
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L100" t="n">
         <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C101" t="n">
         <v>21</v>
@@ -5797,16 +5797,16 @@
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K101" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L101" t="n">
         <v>10</v>
       </c>
       <c r="M101" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N101" t="n">
         <v>0</v>
@@ -5826,13 +5826,13 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C102" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
         <v>7</v>
@@ -5850,7 +5850,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K102" t="n">
         <v>16</v>
@@ -5859,7 +5859,7 @@
         <v>10</v>
       </c>
       <c r="M102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -5879,10 +5879,10 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C103" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D103" t="n">
         <v>6</v>
@@ -5894,22 +5894,22 @@
         <v>18</v>
       </c>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K103" t="n">
         <v>17</v>
       </c>
       <c r="L103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M103" t="n">
         <v>27</v>
@@ -5924,7 +5924,7 @@
         <v>2</v>
       </c>
       <c r="Q103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -5932,37 +5932,37 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C104" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
         <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G104" t="n">
         <v>5</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
         <v>4</v>
       </c>
       <c r="J104" t="n">
+        <v>16</v>
+      </c>
+      <c r="K104" t="n">
         <v>17</v>
       </c>
-      <c r="K104" t="n">
-        <v>18</v>
-      </c>
       <c r="L104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M104" t="n">
         <v>27</v>
@@ -5985,40 +5985,40 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C105" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G105" t="n">
         <v>6</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
         <v>4</v>
       </c>
       <c r="J105" t="n">
+        <v>17</v>
+      </c>
+      <c r="K105" t="n">
         <v>18</v>
-      </c>
-      <c r="K105" t="n">
-        <v>19</v>
       </c>
       <c r="L105" t="n">
         <v>10</v>
       </c>
       <c r="M105" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N105" t="n">
         <v>6</v>
@@ -6038,10 +6038,10 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C106" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D106" t="n">
         <v>7</v>
@@ -6050,7 +6050,7 @@
         <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G106" t="n">
         <v>6</v>
@@ -6059,19 +6059,19 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J106" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K106" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L106" t="n">
         <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N106" t="n">
         <v>5</v>
@@ -6091,10 +6091,10 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C107" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107" t="n">
         <v>7</v>
@@ -6103,7 +6103,7 @@
         <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G107" t="n">
         <v>6</v>
@@ -6115,19 +6115,19 @@
         <v>8</v>
       </c>
       <c r="J107" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K107" t="n">
         <v>19</v>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M107" t="n">
         <v>25</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -6144,19 +6144,19 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C108" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E108" t="n">
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G108" t="n">
         <v>8</v>
@@ -6171,13 +6171,13 @@
         <v>23</v>
       </c>
       <c r="K108" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L108" t="n">
         <v>12</v>
       </c>
       <c r="M108" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N108" t="n">
         <v>5</v>
@@ -6197,13 +6197,13 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C109" t="n">
         <v>30</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
         <v>12</v>
@@ -6215,7 +6215,7 @@
         <v>10</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
         <v>6</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q109" t="n">
         <v>1</v>
@@ -6250,22 +6250,22 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C110" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F110" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H110" t="n">
         <v>1</v>
@@ -6274,19 +6274,19 @@
         <v>6</v>
       </c>
       <c r="J110" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K110" t="n">
         <v>22</v>
       </c>
       <c r="L110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M110" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C111" t="n">
         <v>27</v>
@@ -6321,7 +6321,7 @@
         <v>8</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
         <v>6</v>
@@ -6330,13 +6330,13 @@
         <v>21</v>
       </c>
       <c r="K111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L111" t="n">
         <v>13</v>
       </c>
       <c r="M111" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N111" t="n">
         <v>7</v>
@@ -6356,22 +6356,22 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C112" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D112" t="n">
         <v>8</v>
       </c>
       <c r="E112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F112" t="n">
         <v>27</v>
       </c>
       <c r="G112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -6380,16 +6380,16 @@
         <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K112" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L112" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M112" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N112" t="n">
         <v>5</v>
@@ -6409,19 +6409,19 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C113" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D113" t="n">
         <v>7</v>
       </c>
       <c r="E113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F113" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G113" t="n">
         <v>6</v>
@@ -6433,13 +6433,13 @@
         <v>5</v>
       </c>
       <c r="J113" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M113" t="n">
         <v>23</v>
@@ -6462,19 +6462,19 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C114" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D114" t="n">
         <v>6</v>
       </c>
       <c r="E114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G114" t="n">
         <v>8</v>
@@ -6486,7 +6486,7 @@
         <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K114" t="n">
         <v>22</v>
@@ -6495,7 +6495,7 @@
         <v>11</v>
       </c>
       <c r="M114" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N114" t="n">
         <v>5</v>
@@ -6515,19 +6515,19 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C115" t="n">
         <v>27</v>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F115" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G115" t="n">
         <v>8</v>
@@ -6539,19 +6539,19 @@
         <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M115" t="n">
         <v>24</v>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -6560,7 +6560,7 @@
         <v>6</v>
       </c>
       <c r="Q115" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
@@ -6568,19 +6568,19 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C116" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G116" t="n">
         <v>9</v>
@@ -6592,28 +6592,28 @@
         <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K116" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L116" t="n">
         <v>13</v>
       </c>
       <c r="M116" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P116" t="n">
         <v>6</v>
       </c>
       <c r="Q116" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
@@ -6624,40 +6624,40 @@
         <v>100</v>
       </c>
       <c r="C117" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D117" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E117" t="n">
         <v>17</v>
       </c>
       <c r="F117" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G117" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K117" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L117" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M117" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O117" t="n">
         <v>10</v>
@@ -6666,7 +6666,7 @@
         <v>7</v>
       </c>
       <c r="Q117" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118">
@@ -6674,19 +6674,19 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C118" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E118" t="n">
         <v>18</v>
       </c>
       <c r="F118" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G118" t="n">
         <v>11</v>
@@ -6695,31 +6695,31 @@
         <v>2</v>
       </c>
       <c r="I118" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K118" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L118" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M118" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N118" t="n">
         <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P118" t="n">
         <v>6</v>
       </c>
       <c r="Q118" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
@@ -6727,22 +6727,22 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C119" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F119" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G119" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -6754,13 +6754,13 @@
         <v>27</v>
       </c>
       <c r="K119" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L119" t="n">
         <v>14</v>
       </c>
       <c r="M119" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N119" t="n">
         <v>6</v>
@@ -6769,7 +6769,7 @@
         <v>6</v>
       </c>
       <c r="P119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q119" t="n">
         <v>14</v>
@@ -6780,22 +6780,22 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C120" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D120" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E120" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F120" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G120" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H120" t="n">
         <v>3</v>
@@ -6804,28 +6804,28 @@
         <v>8</v>
       </c>
       <c r="J120" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K120" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L120" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M120" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P120" t="n">
         <v>9</v>
       </c>
       <c r="Q120" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121">
@@ -6833,40 +6833,40 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C121" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D121" t="n">
         <v>12</v>
       </c>
       <c r="E121" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G121" t="n">
         <v>8</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
         <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K121" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L121" t="n">
         <v>14</v>
       </c>
       <c r="M121" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N121" t="n">
         <v>6</v>
@@ -6875,7 +6875,7 @@
         <v>8</v>
       </c>
       <c r="P121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q121" t="n">
         <v>17</v>
@@ -6886,19 +6886,19 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C122" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D122" t="n">
         <v>10</v>
       </c>
       <c r="E122" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F122" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G122" t="n">
         <v>9</v>
@@ -6913,16 +6913,16 @@
         <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L122" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M122" t="n">
         <v>25</v>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O122" t="n">
         <v>6</v>
@@ -6939,25 +6939,25 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C123" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F123" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G123" t="n">
         <v>8</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I123" t="n">
         <v>5</v>
@@ -6966,13 +6966,13 @@
         <v>14</v>
       </c>
       <c r="K123" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L123" t="n">
         <v>12</v>
       </c>
       <c r="M123" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N123" t="n">
         <v>3</v>
@@ -6981,10 +6981,10 @@
         <v>4</v>
       </c>
       <c r="P123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q123" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -6992,40 +6992,40 @@
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E124" t="n">
+        <v>14</v>
+      </c>
+      <c r="F124" t="n">
+        <v>36</v>
+      </c>
+      <c r="G124" t="n">
+        <v>8</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5</v>
+      </c>
+      <c r="J124" t="n">
+        <v>16</v>
+      </c>
+      <c r="K124" t="n">
+        <v>24</v>
+      </c>
+      <c r="L124" t="n">
         <v>13</v>
       </c>
-      <c r="F124" t="n">
-        <v>32</v>
-      </c>
-      <c r="G124" t="n">
-        <v>6</v>
-      </c>
-      <c r="H124" t="n">
-        <v>2</v>
-      </c>
-      <c r="I124" t="n">
-        <v>4</v>
-      </c>
-      <c r="J124" t="n">
-        <v>14</v>
-      </c>
-      <c r="K124" t="n">
-        <v>20</v>
-      </c>
-      <c r="L124" t="n">
-        <v>11</v>
-      </c>
       <c r="M124" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N124" t="n">
         <v>4</v>
@@ -7034,7 +7034,7 @@
         <v>3</v>
       </c>
       <c r="P124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q124" t="n">
         <v>11</v>
@@ -7045,22 +7045,22 @@
         <v>46142</v>
       </c>
       <c r="B125" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C125" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E125" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F125" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G125" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H125" t="n">
         <v>3</v>
@@ -7069,27 +7069,292 @@
         <v>5</v>
       </c>
       <c r="J125" t="n">
+        <v>18</v>
+      </c>
+      <c r="K125" t="n">
+        <v>31</v>
+      </c>
+      <c r="L125" t="n">
+        <v>15</v>
+      </c>
+      <c r="M125" t="n">
+        <v>28</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4</v>
+      </c>
+      <c r="O125" t="n">
+        <v>6</v>
+      </c>
+      <c r="P125" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>80</v>
+      </c>
+      <c r="C126" t="n">
+        <v>43</v>
+      </c>
+      <c r="D126" t="n">
+        <v>18</v>
+      </c>
+      <c r="E126" t="n">
+        <v>14</v>
+      </c>
+      <c r="F126" t="n">
+        <v>40</v>
+      </c>
+      <c r="G126" t="n">
+        <v>9</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" t="n">
+        <v>6</v>
+      </c>
+      <c r="J126" t="n">
+        <v>17</v>
+      </c>
+      <c r="K126" t="n">
+        <v>36</v>
+      </c>
+      <c r="L126" t="n">
+        <v>16</v>
+      </c>
+      <c r="M126" t="n">
+        <v>33</v>
+      </c>
+      <c r="N126" t="n">
+        <v>6</v>
+      </c>
+      <c r="O126" t="n">
+        <v>4</v>
+      </c>
+      <c r="P126" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B127" t="n">
+        <v>81</v>
+      </c>
+      <c r="C127" t="n">
+        <v>39</v>
+      </c>
+      <c r="D127" t="n">
+        <v>15</v>
+      </c>
+      <c r="E127" t="n">
+        <v>16</v>
+      </c>
+      <c r="F127" t="n">
+        <v>44</v>
+      </c>
+      <c r="G127" t="n">
+        <v>10</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5</v>
+      </c>
+      <c r="I127" t="n">
+        <v>6</v>
+      </c>
+      <c r="J127" t="n">
+        <v>18</v>
+      </c>
+      <c r="K127" t="n">
+        <v>33</v>
+      </c>
+      <c r="L127" t="n">
+        <v>21</v>
+      </c>
+      <c r="M127" t="n">
+        <v>39</v>
+      </c>
+      <c r="N127" t="n">
         <v>7</v>
       </c>
-      <c r="K125" t="n">
+      <c r="O127" t="n">
+        <v>4</v>
+      </c>
+      <c r="P127" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B128" t="n">
+        <v>64</v>
+      </c>
+      <c r="C128" t="n">
+        <v>34</v>
+      </c>
+      <c r="D128" t="n">
+        <v>12</v>
+      </c>
+      <c r="E128" t="n">
+        <v>15</v>
+      </c>
+      <c r="F128" t="n">
+        <v>32</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4</v>
+      </c>
+      <c r="I128" t="n">
+        <v>4</v>
+      </c>
+      <c r="J128" t="n">
+        <v>15</v>
+      </c>
+      <c r="K128" t="n">
+        <v>31</v>
+      </c>
+      <c r="L128" t="n">
+        <v>23</v>
+      </c>
+      <c r="M128" t="n">
+        <v>38</v>
+      </c>
+      <c r="N128" t="n">
+        <v>6</v>
+      </c>
+      <c r="O128" t="n">
+        <v>4</v>
+      </c>
+      <c r="P128" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B129" t="n">
+        <v>59</v>
+      </c>
+      <c r="C129" t="n">
+        <v>27</v>
+      </c>
+      <c r="D129" t="n">
+        <v>11</v>
+      </c>
+      <c r="E129" t="n">
+        <v>11</v>
+      </c>
+      <c r="F129" t="n">
+        <v>28</v>
+      </c>
+      <c r="G129" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>13</v>
+      </c>
+      <c r="K129" t="n">
+        <v>31</v>
+      </c>
+      <c r="L129" t="n">
+        <v>15</v>
+      </c>
+      <c r="M129" t="n">
+        <v>25</v>
+      </c>
+      <c r="N129" t="n">
+        <v>3</v>
+      </c>
+      <c r="O129" t="n">
+        <v>5</v>
+      </c>
+      <c r="P129" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B130" t="n">
+        <v>47</v>
+      </c>
+      <c r="C130" t="n">
+        <v>32</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7</v>
+      </c>
+      <c r="E130" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" t="n">
+        <v>26</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>11</v>
+      </c>
+      <c r="K130" t="n">
+        <v>22</v>
+      </c>
+      <c r="L130" t="n">
+        <v>11</v>
+      </c>
+      <c r="M130" t="n">
         <v>19</v>
       </c>
-      <c r="L125" t="n">
-        <v>10</v>
-      </c>
-      <c r="M125" t="n">
-        <v>16</v>
-      </c>
-      <c r="N125" t="n">
+      <c r="N130" t="n">
         <v>3</v>
       </c>
-      <c r="O125" t="n">
-        <v>3</v>
-      </c>
-      <c r="P125" t="n">
+      <c r="O130" t="n">
         <v>4</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="P130" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q130" t="n">
         <v>9</v>
       </c>
     </row>
